--- a/AAII_Financials/Quarterly/HTB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HTB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
   <si>
     <t>HTB</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,88 +656,95 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
-      </c>
-      <c r="H7" s="2">
-        <v>45291</v>
       </c>
       <c r="I7" s="2">
         <v>45291</v>
       </c>
       <c r="J7" s="2">
-        <v>45199</v>
+        <v>45291</v>
       </c>
       <c r="K7" s="2">
         <v>45199</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2">
+        <v>45199</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>49400</v>
+      </c>
+      <c r="E8" s="3">
         <v>52300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>47400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>44900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>48900</v>
-      </c>
-      <c r="H8" s="3">
-        <v>46300</v>
       </c>
       <c r="I8" s="3">
         <v>46300</v>
       </c>
       <c r="J8" s="3">
-        <v>48200</v>
+        <v>46300</v>
       </c>
       <c r="K8" s="3">
         <v>48200</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3">
+        <v>48200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -765,37 +772,43 @@
       <c r="K9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>49400</v>
+      </c>
+      <c r="E10" s="3">
         <v>52300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>47400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>44900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>48900</v>
-      </c>
-      <c r="H10" s="3">
-        <v>46300</v>
       </c>
       <c r="I10" s="3">
         <v>46300</v>
       </c>
       <c r="J10" s="3">
-        <v>48200</v>
+        <v>46300</v>
       </c>
       <c r="K10" s="3">
         <v>48200</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3">
+        <v>48200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -807,8 +820,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -836,8 +850,11 @@
       <c r="K12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -865,66 +882,75 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3">
         <v>-1100</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>-8900</v>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I14" s="3">
         <v>-8900</v>
       </c>
       <c r="J14" s="3">
-        <v>-1100</v>
+        <v>-8900</v>
       </c>
       <c r="K14" s="3">
         <v>-1100</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3">
+        <v>-1100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E15" s="3">
         <v>1400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2800</v>
-      </c>
-      <c r="H15" s="3">
-        <v>3400</v>
       </c>
       <c r="I15" s="3">
         <v>3400</v>
       </c>
       <c r="J15" s="3">
-        <v>2700</v>
+        <v>3400</v>
       </c>
       <c r="K15" s="3">
         <v>2700</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -933,66 +959,73 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E17" s="3">
         <v>32900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>29400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>29100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>28500</v>
-      </c>
-      <c r="H17" s="3">
-        <v>28200</v>
       </c>
       <c r="I17" s="3">
         <v>28200</v>
       </c>
       <c r="J17" s="3">
-        <v>28000</v>
+        <v>28200</v>
       </c>
       <c r="K17" s="3">
         <v>28000</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E18" s="3">
         <v>19400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>18000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>15800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>20300</v>
-      </c>
-      <c r="H18" s="3">
-        <v>18200</v>
       </c>
       <c r="I18" s="3">
         <v>18200</v>
       </c>
       <c r="J18" s="3">
-        <v>20200</v>
+        <v>18200</v>
       </c>
       <c r="K18" s="3">
         <v>20200</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3">
+        <v>20200</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1004,25 +1037,26 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E20" s="3">
         <v>1100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1300</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1600</v>
       </c>
       <c r="I20" s="3">
         <v>1600</v>
@@ -1033,37 +1067,43 @@
       <c r="K20" s="3">
         <v>1600</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E21" s="3">
         <v>19600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>19500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>17100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>21800</v>
-      </c>
-      <c r="H21" s="3">
-        <v>20100</v>
       </c>
       <c r="I21" s="3">
         <v>20100</v>
       </c>
       <c r="J21" s="3">
-        <v>21400</v>
+        <v>20100</v>
       </c>
       <c r="K21" s="3">
         <v>21400</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3">
+        <v>21400</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1091,66 +1131,75 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E23" s="3">
         <v>18300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>16800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>15800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>19000</v>
-      </c>
-      <c r="H23" s="3">
-        <v>25100</v>
       </c>
       <c r="I23" s="3">
         <v>25100</v>
       </c>
       <c r="J23" s="3">
-        <v>18700</v>
+        <v>25100</v>
       </c>
       <c r="K23" s="3">
         <v>18700</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3">
+        <v>18700</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E24" s="3">
         <v>4100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3900</v>
-      </c>
-      <c r="H24" s="3">
-        <v>5100</v>
       </c>
       <c r="I24" s="3">
         <v>5100</v>
       </c>
       <c r="J24" s="3">
-        <v>3800</v>
+        <v>5100</v>
       </c>
       <c r="K24" s="3">
         <v>3800</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1178,66 +1227,75 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E26" s="3">
         <v>14200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>13100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>12400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>15100</v>
-      </c>
-      <c r="H26" s="3">
-        <v>20000</v>
       </c>
       <c r="I26" s="3">
         <v>20000</v>
       </c>
       <c r="J26" s="3">
-        <v>14800</v>
+        <v>20000</v>
       </c>
       <c r="K26" s="3">
         <v>14800</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E27" s="3">
         <v>14100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>13000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>12300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>14900</v>
-      </c>
-      <c r="H27" s="3">
-        <v>19900</v>
       </c>
       <c r="I27" s="3">
         <v>19900</v>
       </c>
       <c r="J27" s="3">
-        <v>14700</v>
+        <v>19900</v>
       </c>
       <c r="K27" s="3">
         <v>14700</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3">
+        <v>14700</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1265,8 +1323,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1294,8 +1355,11 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1323,8 +1387,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1352,25 +1419,28 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1300</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-1600</v>
       </c>
       <c r="I32" s="3">
         <v>-1600</v>
@@ -1381,37 +1451,43 @@
       <c r="K32" s="3">
         <v>-1600</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3">
+        <v>-1600</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E33" s="3">
         <v>14200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>13100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>12400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>15100</v>
-      </c>
-      <c r="H33" s="3">
-        <v>20000</v>
       </c>
       <c r="I33" s="3">
         <v>20000</v>
       </c>
       <c r="J33" s="3">
-        <v>14800</v>
+        <v>20000</v>
       </c>
       <c r="K33" s="3">
         <v>14800</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1439,71 +1515,80 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E35" s="3">
         <v>14200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>13100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>12400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>15100</v>
-      </c>
-      <c r="H35" s="3">
-        <v>20000</v>
       </c>
       <c r="I35" s="3">
         <v>20000</v>
       </c>
       <c r="J35" s="3">
-        <v>14800</v>
+        <v>20000</v>
       </c>
       <c r="K35" s="3">
         <v>14800</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
-      </c>
-      <c r="H38" s="2">
-        <v>45291</v>
       </c>
       <c r="I38" s="2">
         <v>45291</v>
       </c>
       <c r="J38" s="2">
-        <v>45199</v>
+        <v>45291</v>
       </c>
       <c r="K38" s="2">
         <v>45199</v>
       </c>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2">
+        <v>45199</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1515,8 +1600,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1528,66 +1614,73 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>299800</v>
+      </c>
+      <c r="E41" s="3">
         <v>279200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>293500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>294200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>380500</v>
-      </c>
-      <c r="H41" s="3">
-        <v>347100</v>
       </c>
       <c r="I41" s="3">
         <v>347100</v>
       </c>
       <c r="J41" s="3">
-        <v>325000</v>
+        <v>347100</v>
       </c>
       <c r="K41" s="3">
         <v>325000</v>
       </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3">
+        <v>325000</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E42" s="3">
         <v>28500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>29300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>32100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>33600</v>
-      </c>
-      <c r="H42" s="3">
-        <v>34700</v>
       </c>
       <c r="I42" s="3">
         <v>34700</v>
       </c>
       <c r="J42" s="3">
-        <v>35400</v>
+        <v>34700</v>
       </c>
       <c r="K42" s="3">
         <v>35400</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>35400</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1615,8 +1708,11 @@
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1644,8 +1740,11 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1653,13 +1752,13 @@
         <v>18300</v>
       </c>
       <c r="E45" s="3">
+        <v>18300</v>
+      </c>
+      <c r="F45" s="3">
         <v>17500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>18400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>16900</v>
       </c>
       <c r="H45" s="3">
         <v>16900</v>
@@ -1668,129 +1767,144 @@
         <v>16900</v>
       </c>
       <c r="J45" s="3">
-        <v>16500</v>
+        <v>16900</v>
       </c>
       <c r="K45" s="3">
         <v>16500</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>497200</v>
+      </c>
+      <c r="E46" s="3">
         <v>532300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>533000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>571300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>654500</v>
-      </c>
-      <c r="H46" s="3">
-        <v>600600</v>
       </c>
       <c r="I46" s="3">
         <v>600600</v>
       </c>
       <c r="J46" s="3">
-        <v>582400</v>
+        <v>600600</v>
       </c>
       <c r="K46" s="3">
         <v>582400</v>
       </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3">
+        <v>582400</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>181900</v>
+      </c>
+      <c r="E47" s="3">
         <v>170600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>174400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>169200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>149100</v>
-      </c>
-      <c r="H47" s="3">
-        <v>159100</v>
       </c>
       <c r="I47" s="3">
         <v>159100</v>
       </c>
       <c r="J47" s="3">
-        <v>168500</v>
+        <v>159100</v>
       </c>
       <c r="K47" s="3">
         <v>168500</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3">
+        <v>168500</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>78700</v>
+      </c>
+      <c r="E48" s="3">
         <v>109500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>111800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>112900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>109300</v>
-      </c>
-      <c r="H48" s="3">
-        <v>110300</v>
       </c>
       <c r="I48" s="3">
         <v>110300</v>
       </c>
       <c r="J48" s="3">
-        <v>106200</v>
+        <v>110300</v>
       </c>
       <c r="K48" s="3">
         <v>106200</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3">
+        <v>106200</v>
+      </c>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>40200</v>
+      </c>
+      <c r="E49" s="3">
         <v>40700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>41300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>41800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>42400</v>
-      </c>
-      <c r="H49" s="3">
-        <v>43200</v>
       </c>
       <c r="I49" s="3">
         <v>43200</v>
       </c>
       <c r="J49" s="3">
-        <v>44000</v>
+        <v>43200</v>
       </c>
       <c r="K49" s="3">
         <v>44000</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3">
+        <v>44000</v>
+      </c>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1818,8 +1932,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1847,37 +1964,43 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>146900</v>
+      </c>
+      <c r="E52" s="3">
         <v>128600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>115900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>112800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>116900</v>
-      </c>
-      <c r="H52" s="3">
-        <v>195700</v>
       </c>
       <c r="I52" s="3">
         <v>195700</v>
       </c>
       <c r="J52" s="3">
-        <v>128800</v>
+        <v>195700</v>
       </c>
       <c r="K52" s="3">
         <v>128800</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3">
+        <v>128800</v>
+      </c>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1905,37 +2028,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4558100</v>
+      </c>
+      <c r="E54" s="3">
         <v>4595400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4637300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4670900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4684000</v>
-      </c>
-      <c r="H54" s="3">
-        <v>4672600</v>
       </c>
       <c r="I54" s="3">
         <v>4672600</v>
       </c>
       <c r="J54" s="3">
-        <v>4652000</v>
+        <v>4672600</v>
       </c>
       <c r="K54" s="3">
         <v>4652000</v>
       </c>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3">
+        <v>4652000</v>
+      </c>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1947,8 +2076,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1960,66 +2090,73 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3736400</v>
+      </c>
+      <c r="E57" s="3">
         <v>3779200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3761600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3707800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3799800</v>
-      </c>
-      <c r="H57" s="3">
-        <v>3661400</v>
       </c>
       <c r="I57" s="3">
         <v>3661400</v>
       </c>
       <c r="J57" s="3">
-        <v>3641000</v>
+        <v>3661400</v>
       </c>
       <c r="K57" s="3">
         <v>3641000</v>
       </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3">
+        <v>3641000</v>
+      </c>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>178400</v>
+      </c>
+      <c r="E58" s="3">
         <v>189700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>254500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>353800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>277400</v>
-      </c>
-      <c r="H58" s="3">
-        <v>433800</v>
       </c>
       <c r="I58" s="3">
         <v>433800</v>
       </c>
       <c r="J58" s="3">
-        <v>453600</v>
+        <v>433800</v>
       </c>
       <c r="K58" s="3">
         <v>453600</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3">
+        <v>453600</v>
+      </c>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2047,95 +2184,107 @@
       <c r="K59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3914700</v>
+      </c>
+      <c r="E60" s="3">
         <v>3968900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4016000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4061600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4077200</v>
-      </c>
-      <c r="H60" s="3">
-        <v>4095100</v>
       </c>
       <c r="I60" s="3">
         <v>4095100</v>
       </c>
       <c r="J60" s="3">
-        <v>4094600</v>
+        <v>4095100</v>
       </c>
       <c r="K60" s="3">
         <v>4094600</v>
       </c>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3">
+        <v>4094600</v>
+      </c>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E61" s="3">
         <v>18000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>25600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>31100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>34800</v>
-      </c>
-      <c r="H61" s="3">
-        <v>39800</v>
       </c>
       <c r="I61" s="3">
         <v>39800</v>
       </c>
       <c r="J61" s="3">
-        <v>19900</v>
+        <v>39800</v>
       </c>
       <c r="K61" s="3">
         <v>19900</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>19900</v>
+      </c>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>59500</v>
+      </c>
+      <c r="E62" s="3">
         <v>51600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>55700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>54600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>58800</v>
-      </c>
-      <c r="H62" s="3">
-        <v>67600</v>
       </c>
       <c r="I62" s="3">
         <v>67600</v>
       </c>
       <c r="J62" s="3">
-        <v>53100</v>
+        <v>67600</v>
       </c>
       <c r="K62" s="3">
         <v>53100</v>
       </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3">
+        <v>53100</v>
+      </c>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2163,8 +2312,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2192,8 +2344,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2221,37 +2376,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3992600</v>
+      </c>
+      <c r="E66" s="3">
         <v>4043700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4097300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4147200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4170800</v>
-      </c>
-      <c r="H66" s="3">
-        <v>4172700</v>
       </c>
       <c r="I66" s="3">
         <v>4172700</v>
       </c>
       <c r="J66" s="3">
-        <v>4167600</v>
+        <v>4172700</v>
       </c>
       <c r="K66" s="3">
         <v>4167600</v>
       </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3">
+        <v>4167600</v>
+      </c>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2263,8 +2424,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2292,8 +2454,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2321,8 +2486,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2350,8 +2518,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2379,37 +2550,43 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>393000</v>
+      </c>
+      <c r="E72" s="3">
         <v>380500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>368400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>357100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>346600</v>
-      </c>
-      <c r="H72" s="3">
-        <v>333400</v>
       </c>
       <c r="I72" s="3">
         <v>333400</v>
       </c>
       <c r="J72" s="3">
-        <v>321800</v>
+        <v>333400</v>
       </c>
       <c r="K72" s="3">
         <v>321800</v>
       </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3">
+        <v>321800</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2437,8 +2614,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2466,8 +2646,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2495,37 +2678,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>565400</v>
+      </c>
+      <c r="E76" s="3">
         <v>551800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>540000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>523600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>513200</v>
-      </c>
-      <c r="H76" s="3">
-        <v>499900</v>
       </c>
       <c r="I76" s="3">
         <v>499900</v>
       </c>
       <c r="J76" s="3">
-        <v>484400</v>
+        <v>499900</v>
       </c>
       <c r="K76" s="3">
         <v>484400</v>
       </c>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3">
+        <v>484400</v>
+      </c>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2553,71 +2742,80 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
-      </c>
-      <c r="H80" s="2">
-        <v>45291</v>
       </c>
       <c r="I80" s="2">
         <v>45291</v>
       </c>
       <c r="J80" s="2">
-        <v>45199</v>
+        <v>45291</v>
       </c>
       <c r="K80" s="2">
         <v>45199</v>
       </c>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2">
+        <v>45199</v>
+      </c>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E81" s="3">
         <v>14200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>13100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>12400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>15100</v>
-      </c>
-      <c r="H81" s="3">
-        <v>20000</v>
       </c>
       <c r="I81" s="3">
         <v>20000</v>
       </c>
       <c r="J81" s="3">
-        <v>14800</v>
+        <v>20000</v>
       </c>
       <c r="K81" s="3">
         <v>14800</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2629,19 +2827,20 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2700</v>
+        <v>2600</v>
       </c>
       <c r="E83" s="3">
         <v>2700</v>
       </c>
       <c r="F83" s="3">
-        <v>2400</v>
+        <v>2700</v>
       </c>
       <c r="G83" s="3">
         <v>2400</v>
@@ -2653,13 +2852,16 @@
         <v>2400</v>
       </c>
       <c r="J83" s="3">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="K83" s="3">
         <v>2300</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2687,8 +2889,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2716,8 +2921,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2745,8 +2953,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2774,8 +2985,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2803,37 +3017,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>71700</v>
+      </c>
+      <c r="E89" s="3">
         <v>4300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>43800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-9000</v>
-      </c>
-      <c r="H89" s="3">
-        <v>90000</v>
       </c>
       <c r="I89" s="3">
         <v>90000</v>
       </c>
       <c r="J89" s="3">
-        <v>-33000</v>
+        <v>90000</v>
       </c>
       <c r="K89" s="3">
         <v>-33000</v>
       </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3">
+        <v>-33000</v>
+      </c>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2845,37 +3065,41 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4000</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-14700</v>
       </c>
       <c r="I91" s="3">
         <v>-14700</v>
       </c>
       <c r="J91" s="3">
-        <v>-5500</v>
+        <v>-14700</v>
       </c>
       <c r="K91" s="3">
         <v>-5500</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>-5500</v>
+      </c>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2903,8 +3127,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2932,37 +3159,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E94" s="3">
         <v>37500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>6300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-70700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>48100</v>
-      </c>
-      <c r="H94" s="3">
-        <v>89500</v>
       </c>
       <c r="I94" s="3">
         <v>89500</v>
       </c>
       <c r="J94" s="3">
-        <v>21500</v>
+        <v>89500</v>
       </c>
       <c r="K94" s="3">
         <v>21500</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3">
+        <v>21500</v>
+      </c>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2974,8 +3207,9 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -2983,7 +3217,7 @@
         <v>2100</v>
       </c>
       <c r="E96" s="3">
-        <v>1900</v>
+        <v>2100</v>
       </c>
       <c r="F96" s="3">
         <v>1900</v>
@@ -2992,19 +3226,22 @@
         <v>1900</v>
       </c>
       <c r="H96" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="I96" s="3">
         <v>2000</v>
       </c>
       <c r="J96" s="3">
-        <v>1700</v>
+        <v>2000</v>
       </c>
       <c r="K96" s="3">
         <v>1700</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3032,8 +3269,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3061,8 +3301,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3090,37 +3333,43 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-56700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-56000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-50800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-21500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5800</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-252200</v>
       </c>
       <c r="I100" s="3">
         <v>-252200</v>
       </c>
       <c r="J100" s="3">
-        <v>33000</v>
+        <v>-252200</v>
       </c>
       <c r="K100" s="3">
         <v>33000</v>
       </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3148,33 +3397,39 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-14300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-86300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>33400</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-72700</v>
       </c>
       <c r="I102" s="3">
         <v>-72700</v>
       </c>
       <c r="J102" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="K102" s="3">
         <v>21500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>21500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HTB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HTB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
   <si>
     <t>HTB</t>
   </si>
@@ -656,95 +656,102 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
-      </c>
-      <c r="I7" s="2">
-        <v>45291</v>
       </c>
       <c r="J7" s="2">
         <v>45291</v>
       </c>
       <c r="K7" s="2">
-        <v>45199</v>
+        <v>45291</v>
       </c>
       <c r="L7" s="2">
         <v>45199</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2">
+        <v>45199</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>53100</v>
+      </c>
+      <c r="E8" s="3">
         <v>49400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>52300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>47400</v>
       </c>
-      <c r="G8" s="3">
-        <v>44900</v>
-      </c>
       <c r="H8" s="3">
+        <v>46300</v>
+      </c>
+      <c r="I8" s="3">
         <v>48900</v>
-      </c>
-      <c r="I8" s="3">
-        <v>46300</v>
       </c>
       <c r="J8" s="3">
         <v>46300</v>
       </c>
       <c r="K8" s="3">
-        <v>48200</v>
+        <v>46300</v>
       </c>
       <c r="L8" s="3">
         <v>48200</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3">
+        <v>48200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -775,40 +782,46 @@
       <c r="L9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>53100</v>
+      </c>
+      <c r="E10" s="3">
         <v>49400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>52300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>47400</v>
       </c>
-      <c r="G10" s="3">
-        <v>44900</v>
-      </c>
       <c r="H10" s="3">
+        <v>46300</v>
+      </c>
+      <c r="I10" s="3">
         <v>48900</v>
-      </c>
-      <c r="I10" s="3">
-        <v>46300</v>
       </c>
       <c r="J10" s="3">
         <v>46300</v>
       </c>
       <c r="K10" s="3">
-        <v>48200</v>
+        <v>46300</v>
       </c>
       <c r="L10" s="3">
         <v>48200</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3">
+        <v>48200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -821,8 +834,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -853,8 +867,11 @@
       <c r="L12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -885,40 +902,46 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-1100</v>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="3">
-        <v>-8900</v>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J14" s="3">
         <v>-8900</v>
       </c>
       <c r="K14" s="3">
-        <v>-1100</v>
+        <v>-8900</v>
       </c>
       <c r="L14" s="3">
         <v>-1100</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3">
+        <v>-1100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -926,31 +949,34 @@
         <v>2300</v>
       </c>
       <c r="E15" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F15" s="3">
         <v>1400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2800</v>
-      </c>
-      <c r="I15" s="3">
-        <v>3400</v>
       </c>
       <c r="J15" s="3">
         <v>3400</v>
       </c>
       <c r="K15" s="3">
-        <v>2700</v>
+        <v>3400</v>
       </c>
       <c r="L15" s="3">
         <v>2700</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -960,72 +986,79 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E17" s="3">
         <v>29900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>32900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>29400</v>
       </c>
-      <c r="G17" s="3">
-        <v>29100</v>
-      </c>
       <c r="H17" s="3">
+        <v>29400</v>
+      </c>
+      <c r="I17" s="3">
         <v>28500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
+        <v>28000</v>
+      </c>
+      <c r="K17" s="3">
         <v>28200</v>
-      </c>
-      <c r="J17" s="3">
-        <v>28200</v>
-      </c>
-      <c r="K17" s="3">
-        <v>28000</v>
       </c>
       <c r="L17" s="3">
         <v>28000</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E18" s="3">
         <v>19500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>19400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>18000</v>
       </c>
-      <c r="G18" s="3">
-        <v>15800</v>
-      </c>
       <c r="H18" s="3">
+        <v>16900</v>
+      </c>
+      <c r="I18" s="3">
         <v>20300</v>
-      </c>
-      <c r="I18" s="3">
-        <v>18200</v>
       </c>
       <c r="J18" s="3">
         <v>18200</v>
       </c>
       <c r="K18" s="3">
-        <v>20200</v>
+        <v>18200</v>
       </c>
       <c r="L18" s="3">
         <v>20200</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3">
+        <v>20200</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1038,31 +1071,32 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>900</v>
+      </c>
+      <c r="E20" s="3">
         <v>1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1300</v>
       </c>
-      <c r="I20" s="3">
-        <v>1600</v>
-      </c>
       <c r="J20" s="3">
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="K20" s="3">
         <v>1600</v>
@@ -1070,40 +1104,46 @@
       <c r="L20" s="3">
         <v>1600</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E21" s="3">
         <v>20700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>19600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>19500</v>
       </c>
-      <c r="G21" s="3">
-        <v>17100</v>
-      </c>
       <c r="H21" s="3">
+        <v>18200</v>
+      </c>
+      <c r="I21" s="3">
         <v>21800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
+        <v>19600</v>
+      </c>
+      <c r="K21" s="3">
         <v>20100</v>
-      </c>
-      <c r="J21" s="3">
-        <v>20100</v>
-      </c>
-      <c r="K21" s="3">
-        <v>21400</v>
       </c>
       <c r="L21" s="3">
         <v>21400</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3">
+        <v>21400</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1134,72 +1174,81 @@
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E23" s="3">
         <v>18400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>18300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>16800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>15800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>19000</v>
-      </c>
-      <c r="I23" s="3">
-        <v>25100</v>
       </c>
       <c r="J23" s="3">
         <v>25100</v>
       </c>
       <c r="K23" s="3">
-        <v>18700</v>
+        <v>25100</v>
       </c>
       <c r="L23" s="3">
         <v>18700</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3">
+        <v>18700</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E24" s="3">
         <v>3900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3900</v>
-      </c>
-      <c r="I24" s="3">
-        <v>5100</v>
       </c>
       <c r="J24" s="3">
         <v>5100</v>
       </c>
       <c r="K24" s="3">
-        <v>3800</v>
+        <v>5100</v>
       </c>
       <c r="L24" s="3">
         <v>3800</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1230,72 +1279,81 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E26" s="3">
         <v>14500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>14200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>13100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>12400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>15100</v>
-      </c>
-      <c r="I26" s="3">
-        <v>20000</v>
       </c>
       <c r="J26" s="3">
         <v>20000</v>
       </c>
       <c r="K26" s="3">
-        <v>14800</v>
+        <v>20000</v>
       </c>
       <c r="L26" s="3">
         <v>14800</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E27" s="3">
         <v>14400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>14100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>13000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>12300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>14900</v>
-      </c>
-      <c r="I27" s="3">
-        <v>19900</v>
       </c>
       <c r="J27" s="3">
         <v>19900</v>
       </c>
       <c r="K27" s="3">
-        <v>14700</v>
+        <v>19900</v>
       </c>
       <c r="L27" s="3">
         <v>14700</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3">
+        <v>14700</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1326,8 +1384,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1358,8 +1419,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1390,8 +1454,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1422,31 +1489,34 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1300</v>
       </c>
-      <c r="I32" s="3">
-        <v>-1600</v>
-      </c>
       <c r="J32" s="3">
-        <v>-1600</v>
+        <v>-2100</v>
       </c>
       <c r="K32" s="3">
         <v>-1600</v>
@@ -1454,40 +1524,46 @@
       <c r="L32" s="3">
         <v>-1600</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3">
+        <v>-1600</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E33" s="3">
         <v>14500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>14200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>13100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>12400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>15100</v>
-      </c>
-      <c r="I33" s="3">
-        <v>20000</v>
       </c>
       <c r="J33" s="3">
         <v>20000</v>
       </c>
       <c r="K33" s="3">
-        <v>14800</v>
+        <v>20000</v>
       </c>
       <c r="L33" s="3">
         <v>14800</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1518,77 +1594,86 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E35" s="3">
         <v>14500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>14200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>13100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>12400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>15100</v>
-      </c>
-      <c r="I35" s="3">
-        <v>20000</v>
       </c>
       <c r="J35" s="3">
         <v>20000</v>
       </c>
       <c r="K35" s="3">
-        <v>14800</v>
+        <v>20000</v>
       </c>
       <c r="L35" s="3">
         <v>14800</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
-      </c>
-      <c r="I38" s="2">
-        <v>45291</v>
       </c>
       <c r="J38" s="2">
         <v>45291</v>
       </c>
       <c r="K38" s="2">
-        <v>45199</v>
+        <v>45291</v>
       </c>
       <c r="L38" s="2">
         <v>45199</v>
       </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2">
+        <v>45199</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1601,8 +1686,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1615,72 +1701,79 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>297200</v>
+      </c>
+      <c r="E41" s="3">
         <v>299800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>279200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>293500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>294200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>380500</v>
-      </c>
-      <c r="I41" s="3">
-        <v>347100</v>
       </c>
       <c r="J41" s="3">
         <v>347100</v>
       </c>
       <c r="K41" s="3">
-        <v>325000</v>
+        <v>347100</v>
       </c>
       <c r="L41" s="3">
         <v>325000</v>
       </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3">
+        <v>325000</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E42" s="3">
         <v>25800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>28500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>29300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>32100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>33600</v>
-      </c>
-      <c r="I42" s="3">
-        <v>34700</v>
       </c>
       <c r="J42" s="3">
         <v>34700</v>
       </c>
       <c r="K42" s="3">
-        <v>35400</v>
+        <v>34700</v>
       </c>
       <c r="L42" s="3">
         <v>35400</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>35400</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1711,8 +1804,11 @@
       <c r="L43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1743,25 +1839,28 @@
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>18300</v>
+        <v>17200</v>
       </c>
       <c r="E45" s="3">
         <v>18300</v>
       </c>
       <c r="F45" s="3">
+        <v>18300</v>
+      </c>
+      <c r="G45" s="3">
         <v>17500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>18400</v>
-      </c>
-      <c r="H45" s="3">
-        <v>16900</v>
       </c>
       <c r="I45" s="3">
         <v>16900</v>
@@ -1770,141 +1869,156 @@
         <v>16900</v>
       </c>
       <c r="K45" s="3">
-        <v>16500</v>
+        <v>16900</v>
       </c>
       <c r="L45" s="3">
         <v>16500</v>
       </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>508600</v>
+      </c>
+      <c r="E46" s="3">
         <v>497200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>532300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>533000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>571300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>654500</v>
-      </c>
-      <c r="I46" s="3">
-        <v>600600</v>
       </c>
       <c r="J46" s="3">
         <v>600600</v>
       </c>
       <c r="K46" s="3">
-        <v>582400</v>
+        <v>600600</v>
       </c>
       <c r="L46" s="3">
         <v>582400</v>
       </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3">
+        <v>582400</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>176900</v>
+      </c>
+      <c r="E47" s="3">
         <v>181900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>170600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>174400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>169200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>149100</v>
-      </c>
-      <c r="I47" s="3">
-        <v>159100</v>
       </c>
       <c r="J47" s="3">
         <v>159100</v>
       </c>
       <c r="K47" s="3">
-        <v>168500</v>
+        <v>159100</v>
       </c>
       <c r="L47" s="3">
         <v>168500</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3">
+        <v>168500</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>70600</v>
+      </c>
+      <c r="E48" s="3">
         <v>78700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>109500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>111800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>112900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>109300</v>
-      </c>
-      <c r="I48" s="3">
-        <v>110300</v>
       </c>
       <c r="J48" s="3">
         <v>110300</v>
       </c>
       <c r="K48" s="3">
-        <v>106200</v>
+        <v>110300</v>
       </c>
       <c r="L48" s="3">
         <v>106200</v>
       </c>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3">
+        <v>106200</v>
+      </c>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>39800</v>
+      </c>
+      <c r="E49" s="3">
         <v>40200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>40700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>41300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>41800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>42400</v>
-      </c>
-      <c r="I49" s="3">
-        <v>43200</v>
       </c>
       <c r="J49" s="3">
         <v>43200</v>
       </c>
       <c r="K49" s="3">
-        <v>44000</v>
+        <v>43200</v>
       </c>
       <c r="L49" s="3">
         <v>44000</v>
       </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3">
+        <v>44000</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1935,8 +2049,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1967,40 +2084,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>144300</v>
+      </c>
+      <c r="E52" s="3">
         <v>146900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>128600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>115900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>112800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>116900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
+        <v>156300</v>
+      </c>
+      <c r="K52" s="3">
         <v>195700</v>
-      </c>
-      <c r="J52" s="3">
-        <v>195700</v>
-      </c>
-      <c r="K52" s="3">
-        <v>128800</v>
       </c>
       <c r="L52" s="3">
         <v>128800</v>
       </c>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3">
+        <v>128800</v>
+      </c>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2031,40 +2154,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4578100</v>
+      </c>
+      <c r="E54" s="3">
         <v>4558100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4595400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4637300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4670900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4684000</v>
-      </c>
-      <c r="I54" s="3">
-        <v>4672600</v>
       </c>
       <c r="J54" s="3">
         <v>4672600</v>
       </c>
       <c r="K54" s="3">
-        <v>4652000</v>
+        <v>4672600</v>
       </c>
       <c r="L54" s="3">
         <v>4652000</v>
       </c>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3">
+        <v>4652000</v>
+      </c>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2077,8 +2206,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2091,72 +2221,79 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3666200</v>
+      </c>
+      <c r="E57" s="3">
         <v>3736400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3779200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3761600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3707800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3799800</v>
-      </c>
-      <c r="I57" s="3">
-        <v>3661400</v>
       </c>
       <c r="J57" s="3">
         <v>3661400</v>
       </c>
       <c r="K57" s="3">
-        <v>3641000</v>
+        <v>3661400</v>
       </c>
       <c r="L57" s="3">
         <v>3641000</v>
       </c>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3">
+        <v>3641000</v>
+      </c>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>265900</v>
+      </c>
+      <c r="E58" s="3">
         <v>178400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>189700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>254500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>353800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>277400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
+        <v>415000</v>
+      </c>
+      <c r="K58" s="3">
         <v>433800</v>
-      </c>
-      <c r="J58" s="3">
-        <v>433800</v>
-      </c>
-      <c r="K58" s="3">
-        <v>453600</v>
       </c>
       <c r="L58" s="3">
         <v>453600</v>
       </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3">
+        <v>453600</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2187,104 +2324,116 @@
       <c r="L59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3932100</v>
+      </c>
+      <c r="E60" s="3">
         <v>3914700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3968900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4016000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4061600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4077200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
+        <v>4076400</v>
+      </c>
+      <c r="K60" s="3">
         <v>4095100</v>
-      </c>
-      <c r="J60" s="3">
-        <v>4095100</v>
-      </c>
-      <c r="K60" s="3">
-        <v>4094600</v>
       </c>
       <c r="L60" s="3">
         <v>4094600</v>
       </c>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3">
+        <v>4094600</v>
+      </c>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E61" s="3">
         <v>18400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>25600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>31100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>34800</v>
-      </c>
-      <c r="I61" s="3">
-        <v>39800</v>
       </c>
       <c r="J61" s="3">
         <v>39800</v>
       </c>
       <c r="K61" s="3">
-        <v>19900</v>
+        <v>39800</v>
       </c>
       <c r="L61" s="3">
         <v>19900</v>
       </c>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>19900</v>
+      </c>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E62" s="3">
         <v>59500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>51600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>55700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>54600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>58800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
+        <v>51300</v>
+      </c>
+      <c r="K62" s="3">
         <v>67600</v>
-      </c>
-      <c r="J62" s="3">
-        <v>67600</v>
-      </c>
-      <c r="K62" s="3">
-        <v>53100</v>
       </c>
       <c r="L62" s="3">
         <v>53100</v>
       </c>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3">
+        <v>53100</v>
+      </c>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2315,8 +2464,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2347,8 +2499,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2379,40 +2534,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3998800</v>
+      </c>
+      <c r="E66" s="3">
         <v>3992600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4043700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4097300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4147200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4170800</v>
-      </c>
-      <c r="I66" s="3">
-        <v>4172700</v>
       </c>
       <c r="J66" s="3">
         <v>4172700</v>
       </c>
       <c r="K66" s="3">
-        <v>4167600</v>
+        <v>4172700</v>
       </c>
       <c r="L66" s="3">
         <v>4167600</v>
       </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3">
+        <v>4167600</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2425,8 +2586,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2457,8 +2619,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2489,8 +2654,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2521,8 +2689,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2553,40 +2724,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>408200</v>
+      </c>
+      <c r="E72" s="3">
         <v>393000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>380500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>368400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>357100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>346600</v>
-      </c>
-      <c r="I72" s="3">
-        <v>333400</v>
       </c>
       <c r="J72" s="3">
         <v>333400</v>
       </c>
       <c r="K72" s="3">
-        <v>321800</v>
+        <v>333400</v>
       </c>
       <c r="L72" s="3">
         <v>321800</v>
       </c>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3">
+        <v>321800</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2617,8 +2794,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2649,8 +2829,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2681,40 +2864,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>579300</v>
+      </c>
+      <c r="E76" s="3">
         <v>565400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>551800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>540000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>523600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>513200</v>
-      </c>
-      <c r="I76" s="3">
-        <v>499900</v>
       </c>
       <c r="J76" s="3">
         <v>499900</v>
       </c>
       <c r="K76" s="3">
-        <v>484400</v>
+        <v>499900</v>
       </c>
       <c r="L76" s="3">
         <v>484400</v>
       </c>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3">
+        <v>484400</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2745,77 +2934,86 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
-      </c>
-      <c r="I80" s="2">
-        <v>45291</v>
       </c>
       <c r="J80" s="2">
         <v>45291</v>
       </c>
       <c r="K80" s="2">
-        <v>45199</v>
+        <v>45291</v>
       </c>
       <c r="L80" s="2">
         <v>45199</v>
       </c>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2">
+        <v>45199</v>
+      </c>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E81" s="3">
         <v>14500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>14200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>13100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>12400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>15100</v>
-      </c>
-      <c r="I81" s="3">
-        <v>20000</v>
       </c>
       <c r="J81" s="3">
         <v>20000</v>
       </c>
       <c r="K81" s="3">
-        <v>14800</v>
+        <v>20000</v>
       </c>
       <c r="L81" s="3">
         <v>14800</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2828,22 +3026,23 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2600</v>
-      </c>
-      <c r="E83" s="3">
-        <v>2700</v>
       </c>
       <c r="F83" s="3">
         <v>2700</v>
       </c>
       <c r="G83" s="3">
-        <v>2400</v>
+        <v>2700</v>
       </c>
       <c r="H83" s="3">
         <v>2400</v>
@@ -2855,13 +3054,16 @@
         <v>2400</v>
       </c>
       <c r="K83" s="3">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="L83" s="3">
         <v>2300</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2892,8 +3094,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2924,8 +3129,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2956,8 +3164,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2988,8 +3199,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3020,40 +3234,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E89" s="3">
         <v>71700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>43800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-9000</v>
-      </c>
-      <c r="I89" s="3">
-        <v>90000</v>
       </c>
       <c r="J89" s="3">
         <v>90000</v>
       </c>
       <c r="K89" s="3">
-        <v>-33000</v>
+        <v>90000</v>
       </c>
       <c r="L89" s="3">
         <v>-33000</v>
       </c>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3">
+        <v>-33000</v>
+      </c>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3066,40 +3286,44 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4000</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-14700</v>
       </c>
       <c r="J91" s="3">
         <v>-14700</v>
       </c>
       <c r="K91" s="3">
-        <v>-5500</v>
+        <v>-14700</v>
       </c>
       <c r="L91" s="3">
         <v>-5500</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>-5500</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3130,8 +3354,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3162,40 +3389,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E94" s="3">
         <v>5600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>37500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>6300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-70700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>48100</v>
-      </c>
-      <c r="I94" s="3">
-        <v>89500</v>
       </c>
       <c r="J94" s="3">
         <v>89500</v>
       </c>
       <c r="K94" s="3">
-        <v>21500</v>
+        <v>89500</v>
       </c>
       <c r="L94" s="3">
         <v>21500</v>
       </c>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3">
+        <v>21500</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3208,8 +3441,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3220,7 +3454,7 @@
         <v>2100</v>
       </c>
       <c r="F96" s="3">
-        <v>1900</v>
+        <v>2100</v>
       </c>
       <c r="G96" s="3">
         <v>1900</v>
@@ -3229,19 +3463,22 @@
         <v>1900</v>
       </c>
       <c r="I96" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="J96" s="3">
         <v>2000</v>
       </c>
       <c r="K96" s="3">
-        <v>1700</v>
+        <v>2000</v>
       </c>
       <c r="L96" s="3">
         <v>1700</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3272,8 +3509,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3304,8 +3544,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3336,40 +3579,46 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-56700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-56000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-50800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-21500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5800</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-252200</v>
       </c>
       <c r="J100" s="3">
         <v>-252200</v>
       </c>
       <c r="K100" s="3">
-        <v>33000</v>
+        <v>-252200</v>
       </c>
       <c r="L100" s="3">
         <v>33000</v>
       </c>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3400,36 +3649,42 @@
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E102" s="3">
         <v>20600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-14300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-86300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>33400</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-72700</v>
       </c>
       <c r="J102" s="3">
         <v>-72700</v>
       </c>
       <c r="K102" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="L102" s="3">
         <v>21500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>21500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HTB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HTB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="92">
   <si>
     <t>HTB</t>
   </si>
@@ -656,109 +656,115 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
-      </c>
-      <c r="K7" s="2">
-        <v>45291</v>
       </c>
       <c r="L7" s="2">
         <v>45291</v>
       </c>
       <c r="M7" s="2">
-        <v>45199</v>
+        <v>45291</v>
       </c>
       <c r="N7" s="2">
         <v>45199</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2">
+        <v>45199</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>51400</v>
+      </c>
+      <c r="E8" s="3">
         <v>52100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>53100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>49400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>52300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>47700</v>
       </c>
-      <c r="I8" s="3">
-        <v>46600</v>
-      </c>
       <c r="J8" s="3">
+        <v>46300</v>
+      </c>
+      <c r="K8" s="3">
         <v>48900</v>
-      </c>
-      <c r="K8" s="3">
-        <v>46300</v>
       </c>
       <c r="L8" s="3">
         <v>46300</v>
       </c>
       <c r="M8" s="3">
-        <v>48200</v>
+        <v>46300</v>
       </c>
       <c r="N8" s="3">
         <v>48200</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3">
+        <v>48200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -795,46 +801,52 @@
       <c r="N9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>51400</v>
+      </c>
+      <c r="E10" s="3">
         <v>52100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>53100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>49400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>52300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>47700</v>
       </c>
-      <c r="I10" s="3">
-        <v>46600</v>
-      </c>
       <c r="J10" s="3">
+        <v>46300</v>
+      </c>
+      <c r="K10" s="3">
         <v>48900</v>
-      </c>
-      <c r="K10" s="3">
-        <v>46300</v>
       </c>
       <c r="L10" s="3">
         <v>46300</v>
       </c>
       <c r="M10" s="3">
-        <v>48200</v>
+        <v>46300</v>
       </c>
       <c r="N10" s="3">
         <v>48200</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3">
+        <v>48200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -849,8 +861,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -887,8 +900,11 @@
       <c r="N12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -925,13 +941,16 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>-100</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>5</v>
@@ -939,11 +958,11 @@
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>5</v>
@@ -951,58 +970,64 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>-8900</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>-8900</v>
       </c>
       <c r="M14" s="3">
-        <v>-1100</v>
+        <v>-8900</v>
       </c>
       <c r="N14" s="3">
         <v>-1100</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>-1100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E15" s="3">
         <v>1400</v>
-      </c>
-      <c r="E15" s="3">
-        <v>2300</v>
       </c>
       <c r="F15" s="3">
         <v>2300</v>
       </c>
       <c r="G15" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H15" s="3">
         <v>1400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2800</v>
-      </c>
-      <c r="K15" s="3">
-        <v>3400</v>
       </c>
       <c r="L15" s="3">
         <v>3400</v>
       </c>
       <c r="M15" s="3">
-        <v>2700</v>
+        <v>3400</v>
       </c>
       <c r="N15" s="3">
         <v>2700</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1014,84 +1039,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>30400</v>
+        <v>30800</v>
       </c>
       <c r="E17" s="3">
         <v>30400</v>
       </c>
       <c r="F17" s="3">
+        <v>30400</v>
+      </c>
+      <c r="G17" s="3">
         <v>29900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>32900</v>
-      </c>
-      <c r="H17" s="3">
-        <v>29700</v>
       </c>
       <c r="I17" s="3">
         <v>29700</v>
       </c>
       <c r="J17" s="3">
+        <v>29400</v>
+      </c>
+      <c r="K17" s="3">
         <v>28500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>28000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>28200</v>
-      </c>
-      <c r="M17" s="3">
-        <v>28000</v>
       </c>
       <c r="N17" s="3">
         <v>28000</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E18" s="3">
         <v>21700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>22700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>19500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>19400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>18000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>16900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>20300</v>
-      </c>
-      <c r="K18" s="3">
-        <v>18200</v>
       </c>
       <c r="L18" s="3">
         <v>18200</v>
       </c>
       <c r="M18" s="3">
-        <v>20200</v>
+        <v>18200</v>
       </c>
       <c r="N18" s="3">
         <v>20200</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3">
+        <v>20200</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1106,8 +1138,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1118,25 +1151,25 @@
         <v>900</v>
       </c>
       <c r="F20" s="3">
+        <v>900</v>
+      </c>
+      <c r="G20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2100</v>
-      </c>
-      <c r="L20" s="3">
-        <v>1600</v>
       </c>
       <c r="M20" s="3">
         <v>1600</v>
@@ -1144,46 +1177,52 @@
       <c r="N20" s="3">
         <v>1600</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E21" s="3">
         <v>22200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>24100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>20700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>19600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>19500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>18200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>21800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>19600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>20100</v>
-      </c>
-      <c r="M21" s="3">
-        <v>21400</v>
       </c>
       <c r="N21" s="3">
         <v>21400</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3">
+        <v>21400</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1220,84 +1259,93 @@
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E23" s="3">
         <v>20900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>21800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>18400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>18300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>16800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>15800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>19000</v>
-      </c>
-      <c r="K23" s="3">
-        <v>25100</v>
       </c>
       <c r="L23" s="3">
         <v>25100</v>
       </c>
       <c r="M23" s="3">
-        <v>18700</v>
+        <v>25100</v>
       </c>
       <c r="N23" s="3">
         <v>18700</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3">
+        <v>18700</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E24" s="3">
         <v>4400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3900</v>
-      </c>
-      <c r="K24" s="3">
-        <v>5100</v>
       </c>
       <c r="L24" s="3">
         <v>5100</v>
       </c>
       <c r="M24" s="3">
-        <v>3800</v>
+        <v>5100</v>
       </c>
       <c r="N24" s="3">
         <v>3800</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1334,84 +1382,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E26" s="3">
         <v>16500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>17200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>14500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>14200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>13100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>12400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>15100</v>
-      </c>
-      <c r="K26" s="3">
-        <v>20000</v>
       </c>
       <c r="L26" s="3">
         <v>20000</v>
       </c>
       <c r="M26" s="3">
-        <v>14800</v>
+        <v>20000</v>
       </c>
       <c r="N26" s="3">
         <v>14800</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E27" s="3">
         <v>16300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>17000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>14400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>14100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>13000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>12300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>14900</v>
-      </c>
-      <c r="K27" s="3">
-        <v>19900</v>
       </c>
       <c r="L27" s="3">
         <v>19900</v>
       </c>
       <c r="M27" s="3">
-        <v>14700</v>
+        <v>19900</v>
       </c>
       <c r="N27" s="3">
         <v>14700</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3">
+        <v>14700</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1448,8 +1505,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1486,8 +1546,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1524,8 +1587,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1562,8 +1628,11 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1574,25 +1643,25 @@
         <v>-900</v>
       </c>
       <c r="F32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-1600</v>
       </c>
       <c r="M32" s="3">
         <v>-1600</v>
@@ -1600,46 +1669,52 @@
       <c r="N32" s="3">
         <v>-1600</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3">
+        <v>-1600</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E33" s="3">
         <v>16500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>17200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>14500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>14200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>13100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>12400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>15100</v>
-      </c>
-      <c r="K33" s="3">
-        <v>20000</v>
       </c>
       <c r="L33" s="3">
         <v>20000</v>
       </c>
       <c r="M33" s="3">
-        <v>14800</v>
+        <v>20000</v>
       </c>
       <c r="N33" s="3">
         <v>14800</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1676,89 +1751,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E35" s="3">
         <v>16500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>17200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>14500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>14200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>13100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>12400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>15100</v>
-      </c>
-      <c r="K35" s="3">
-        <v>20000</v>
       </c>
       <c r="L35" s="3">
         <v>20000</v>
       </c>
       <c r="M35" s="3">
-        <v>14800</v>
+        <v>20000</v>
       </c>
       <c r="N35" s="3">
         <v>14800</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
-      </c>
-      <c r="K38" s="2">
-        <v>45291</v>
       </c>
       <c r="L38" s="2">
         <v>45291</v>
       </c>
       <c r="M38" s="2">
-        <v>45199</v>
+        <v>45291</v>
       </c>
       <c r="N38" s="2">
         <v>45199</v>
       </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2">
+        <v>45199</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1773,8 +1857,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1789,84 +1874,91 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>324700</v>
+      </c>
+      <c r="E41" s="3">
         <v>315800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>297200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>299800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>279200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>293500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>294200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>380500</v>
-      </c>
-      <c r="K41" s="3">
-        <v>347100</v>
       </c>
       <c r="L41" s="3">
         <v>347100</v>
       </c>
       <c r="M41" s="3">
-        <v>325000</v>
+        <v>347100</v>
       </c>
       <c r="N41" s="3">
         <v>325000</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3">
+        <v>325000</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E42" s="3">
         <v>20800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>23300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>25800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>28500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>29300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>32100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>33600</v>
-      </c>
-      <c r="K42" s="3">
-        <v>34700</v>
       </c>
       <c r="L42" s="3">
         <v>34700</v>
       </c>
       <c r="M42" s="3">
-        <v>35400</v>
+        <v>34700</v>
       </c>
       <c r="N42" s="3">
         <v>35400</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>35400</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1903,8 +1995,11 @@
       <c r="N43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1941,31 +2036,34 @@
       <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E45" s="3">
         <v>17700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>17200</v>
-      </c>
-      <c r="F45" s="3">
-        <v>18300</v>
       </c>
       <c r="G45" s="3">
         <v>18300</v>
       </c>
       <c r="H45" s="3">
+        <v>18300</v>
+      </c>
+      <c r="I45" s="3">
         <v>17500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>18400</v>
-      </c>
-      <c r="J45" s="3">
-        <v>16900</v>
       </c>
       <c r="K45" s="3">
         <v>16900</v>
@@ -1974,165 +2072,180 @@
         <v>16900</v>
       </c>
       <c r="M45" s="3">
-        <v>16500</v>
+        <v>16900</v>
       </c>
       <c r="N45" s="3">
         <v>16500</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>565200</v>
+      </c>
+      <c r="E46" s="3">
         <v>551300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>508600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>497200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>532300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>533000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>571300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>654500</v>
-      </c>
-      <c r="K46" s="3">
-        <v>600600</v>
       </c>
       <c r="L46" s="3">
         <v>600600</v>
       </c>
       <c r="M46" s="3">
-        <v>582400</v>
+        <v>600600</v>
       </c>
       <c r="N46" s="3">
         <v>582400</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3">
+        <v>582400</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>164800</v>
+      </c>
+      <c r="E47" s="3">
         <v>178400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>176900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>181900</v>
       </c>
-      <c r="G47" s="3">
-        <v>170600</v>
-      </c>
       <c r="H47" s="3">
+        <v>180800</v>
+      </c>
+      <c r="I47" s="3">
         <v>174400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>169200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>149100</v>
-      </c>
-      <c r="K47" s="3">
-        <v>159100</v>
       </c>
       <c r="L47" s="3">
         <v>159100</v>
       </c>
       <c r="M47" s="3">
-        <v>168500</v>
+        <v>159100</v>
       </c>
       <c r="N47" s="3">
         <v>168500</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>168500</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>70400</v>
+        <v>95400</v>
       </c>
       <c r="E48" s="3">
+        <v>97600</v>
+      </c>
+      <c r="F48" s="3">
         <v>70600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>78700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>109500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>111800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>112900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>109300</v>
-      </c>
-      <c r="K48" s="3">
-        <v>110300</v>
       </c>
       <c r="L48" s="3">
         <v>110300</v>
       </c>
       <c r="M48" s="3">
-        <v>106200</v>
+        <v>110300</v>
       </c>
       <c r="N48" s="3">
         <v>106200</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3">
+        <v>106200</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E49" s="3">
         <v>39400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>39800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>40200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>40700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>41300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>41800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>42400</v>
-      </c>
-      <c r="K49" s="3">
-        <v>43200</v>
       </c>
       <c r="L49" s="3">
         <v>43200</v>
       </c>
       <c r="M49" s="3">
-        <v>44000</v>
+        <v>43200</v>
       </c>
       <c r="N49" s="3">
         <v>44000</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>44000</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2169,8 +2282,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2207,46 +2323,52 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>142400</v>
+        <v>134700</v>
       </c>
       <c r="E52" s="3">
+        <v>115100</v>
+      </c>
+      <c r="F52" s="3">
         <v>144300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>146900</v>
       </c>
-      <c r="G52" s="3">
-        <v>128600</v>
-      </c>
       <c r="H52" s="3">
+        <v>118400</v>
+      </c>
+      <c r="I52" s="3">
         <v>115900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>112800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>116900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>156300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>195700</v>
-      </c>
-      <c r="M52" s="3">
-        <v>128800</v>
       </c>
       <c r="N52" s="3">
         <v>128800</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3">
+        <v>128800</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2283,46 +2405,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4545600</v>
+      </c>
+      <c r="E54" s="3">
         <v>4592100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4578100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4558100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4595400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4637300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4670900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4684000</v>
-      </c>
-      <c r="K54" s="3">
-        <v>4672600</v>
       </c>
       <c r="L54" s="3">
         <v>4672600</v>
       </c>
       <c r="M54" s="3">
-        <v>4652000</v>
+        <v>4672600</v>
       </c>
       <c r="N54" s="3">
         <v>4652000</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3">
+        <v>4652000</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2337,8 +2465,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2353,84 +2482,91 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3710000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3698200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3666200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3736400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3779200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3761600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3707800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3799800</v>
-      </c>
-      <c r="K57" s="3">
-        <v>3661400</v>
       </c>
       <c r="L57" s="3">
         <v>3661400</v>
       </c>
       <c r="M57" s="3">
-        <v>3641000</v>
+        <v>3661400</v>
       </c>
       <c r="N57" s="3">
         <v>3641000</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3">
+        <v>3641000</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>166900</v>
+      </c>
+      <c r="E58" s="3">
         <v>230500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>265900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>178400</v>
       </c>
-      <c r="G58" s="3">
-        <v>189700</v>
-      </c>
       <c r="H58" s="3">
+        <v>188000</v>
+      </c>
+      <c r="I58" s="3">
         <v>254500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>353800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>277400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>415000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>433800</v>
-      </c>
-      <c r="M58" s="3">
-        <v>453600</v>
       </c>
       <c r="N58" s="3">
         <v>453600</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>453600</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2467,122 +2603,134 @@
       <c r="N59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3876900</v>
+      </c>
+      <c r="E60" s="3">
         <v>3928700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3932100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3914700</v>
       </c>
-      <c r="G60" s="3">
-        <v>3968900</v>
-      </c>
       <c r="H60" s="3">
+        <v>3967200</v>
+      </c>
+      <c r="I60" s="3">
         <v>4016000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4061600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4077200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4076400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4095100</v>
-      </c>
-      <c r="M60" s="3">
-        <v>4094600</v>
       </c>
       <c r="N60" s="3">
         <v>4094600</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3">
+        <v>4094600</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E61" s="3">
         <v>19200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>18400</v>
       </c>
-      <c r="G61" s="3">
-        <v>18000</v>
-      </c>
       <c r="H61" s="3">
+        <v>19700</v>
+      </c>
+      <c r="I61" s="3">
         <v>25600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>31100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>34800</v>
-      </c>
-      <c r="K61" s="3">
-        <v>39800</v>
       </c>
       <c r="L61" s="3">
         <v>39800</v>
       </c>
       <c r="M61" s="3">
-        <v>19900</v>
+        <v>39800</v>
       </c>
       <c r="N61" s="3">
         <v>19900</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>19900</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E62" s="3">
         <v>48400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>48000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>59500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>51600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>55700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>54600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>58800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>51300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>67600</v>
-      </c>
-      <c r="M62" s="3">
-        <v>53100</v>
       </c>
       <c r="N62" s="3">
         <v>53100</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3">
+        <v>53100</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2619,8 +2767,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2657,8 +2808,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2695,46 +2849,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3944900</v>
+      </c>
+      <c r="E66" s="3">
         <v>3996300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3998800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3992600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4043700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4097300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4147200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4170800</v>
-      </c>
-      <c r="K66" s="3">
-        <v>4172700</v>
       </c>
       <c r="L66" s="3">
         <v>4172700</v>
       </c>
       <c r="M66" s="3">
-        <v>4167600</v>
+        <v>4172700</v>
       </c>
       <c r="N66" s="3">
         <v>4167600</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3">
+        <v>4167600</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2749,8 +2909,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2787,8 +2948,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2825,8 +2989,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2863,8 +3030,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2901,46 +3071,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>436500</v>
+      </c>
+      <c r="E72" s="3">
         <v>422600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>408200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>393000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>380500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>368400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>357100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>346600</v>
-      </c>
-      <c r="K72" s="3">
-        <v>333400</v>
       </c>
       <c r="L72" s="3">
         <v>333400</v>
       </c>
       <c r="M72" s="3">
-        <v>321800</v>
+        <v>333400</v>
       </c>
       <c r="N72" s="3">
         <v>321800</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3">
+        <v>321800</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2977,8 +3153,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3015,8 +3194,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3053,46 +3235,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>600700</v>
+      </c>
+      <c r="E76" s="3">
         <v>595800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>579300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>565400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>551800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>540000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>523600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>513200</v>
-      </c>
-      <c r="K76" s="3">
-        <v>499900</v>
       </c>
       <c r="L76" s="3">
         <v>499900</v>
       </c>
       <c r="M76" s="3">
-        <v>484400</v>
+        <v>499900</v>
       </c>
       <c r="N76" s="3">
         <v>484400</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3">
+        <v>484400</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3129,89 +3317,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
-      </c>
-      <c r="K80" s="2">
-        <v>45291</v>
       </c>
       <c r="L80" s="2">
         <v>45291</v>
       </c>
       <c r="M80" s="2">
-        <v>45199</v>
+        <v>45291</v>
       </c>
       <c r="N80" s="2">
         <v>45199</v>
       </c>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2">
+        <v>45199</v>
+      </c>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E81" s="3">
         <v>16500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>17200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>14500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>14200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>13100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>12400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>15100</v>
-      </c>
-      <c r="K81" s="3">
-        <v>20000</v>
       </c>
       <c r="L81" s="3">
         <v>20000</v>
       </c>
       <c r="M81" s="3">
-        <v>14800</v>
+        <v>20000</v>
       </c>
       <c r="N81" s="3">
         <v>14800</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3226,25 +3423,26 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="E83" s="3">
         <v>3000</v>
       </c>
       <c r="F83" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G83" s="3">
         <v>2600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2700</v>
-      </c>
-      <c r="H83" s="3">
-        <v>2400</v>
       </c>
       <c r="I83" s="3">
         <v>2400</v>
@@ -3259,13 +3457,16 @@
         <v>2400</v>
       </c>
       <c r="M83" s="3">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="N83" s="3">
         <v>2300</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3302,8 +3503,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3340,8 +3544,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3378,8 +3585,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3416,8 +3626,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3454,46 +3667,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-11300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-8800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>71700</v>
       </c>
-      <c r="G89" s="3">
-        <v>4300</v>
-      </c>
       <c r="H89" s="3">
+        <v>4800</v>
+      </c>
+      <c r="I89" s="3">
         <v>43800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-9000</v>
-      </c>
-      <c r="K89" s="3">
-        <v>90000</v>
       </c>
       <c r="L89" s="3">
         <v>90000</v>
       </c>
       <c r="M89" s="3">
-        <v>-33000</v>
+        <v>90000</v>
       </c>
       <c r="N89" s="3">
         <v>-33000</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3">
+        <v>-33000</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3508,46 +3727,50 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
-        <v>-1800</v>
-      </c>
       <c r="F91" s="3">
-        <v>-3100</v>
+        <v>-1300</v>
       </c>
       <c r="G91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H91" s="3">
         <v>-1500</v>
       </c>
-      <c r="H91" s="3">
-        <v>-3900</v>
-      </c>
       <c r="I91" s="3">
-        <v>-7300</v>
+        <v>-700</v>
       </c>
       <c r="J91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K91" s="3">
         <v>-4000</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-14700</v>
       </c>
       <c r="L91" s="3">
         <v>-14700</v>
       </c>
       <c r="M91" s="3">
-        <v>-5500</v>
+        <v>-14700</v>
       </c>
       <c r="N91" s="3">
         <v>-5500</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>-5500</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3584,8 +3807,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3622,46 +3848,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E94" s="3">
         <v>34500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>5600</v>
       </c>
-      <c r="G94" s="3">
-        <v>37500</v>
-      </c>
       <c r="H94" s="3">
+        <v>37000</v>
+      </c>
+      <c r="I94" s="3">
         <v>6300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-70700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>48100</v>
-      </c>
-      <c r="K94" s="3">
-        <v>89500</v>
       </c>
       <c r="L94" s="3">
         <v>89500</v>
       </c>
       <c r="M94" s="3">
-        <v>21500</v>
+        <v>89500</v>
       </c>
       <c r="N94" s="3">
         <v>21500</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3">
+        <v>21500</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3676,13 +3908,14 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="E96" s="3">
         <v>2100</v>
@@ -3694,7 +3927,7 @@
         <v>2100</v>
       </c>
       <c r="H96" s="3">
-        <v>1900</v>
+        <v>2100</v>
       </c>
       <c r="I96" s="3">
         <v>1900</v>
@@ -3703,19 +3936,22 @@
         <v>1900</v>
       </c>
       <c r="K96" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="L96" s="3">
         <v>2000</v>
       </c>
       <c r="M96" s="3">
-        <v>1700</v>
+        <v>2000</v>
       </c>
       <c r="N96" s="3">
         <v>1700</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3752,8 +3988,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3790,8 +4029,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3828,46 +4070,52 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-65900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>13100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-56700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-56000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-50800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-21500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5800</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-252200</v>
       </c>
       <c r="L100" s="3">
         <v>-252200</v>
       </c>
       <c r="M100" s="3">
-        <v>33000</v>
+        <v>-252200</v>
       </c>
       <c r="N100" s="3">
         <v>33000</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3904,42 +4152,48 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E102" s="3">
         <v>18600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>20600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-14300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-86300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>33400</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-72700</v>
       </c>
       <c r="L102" s="3">
         <v>-72700</v>
       </c>
       <c r="M102" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="N102" s="3">
         <v>21500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>21500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HTB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HTB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
   <si>
     <t>HTB</t>
   </si>
@@ -656,115 +656,122 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
-      </c>
-      <c r="L7" s="2">
-        <v>45291</v>
       </c>
       <c r="M7" s="2">
         <v>45291</v>
       </c>
       <c r="N7" s="2">
-        <v>45199</v>
+        <v>45291</v>
       </c>
       <c r="O7" s="2">
         <v>45199</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2">
+        <v>45199</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E8" s="3">
         <v>51400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>52100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>53100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>49400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>52300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>47700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>46300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>48900</v>
-      </c>
-      <c r="L8" s="3">
-        <v>46300</v>
       </c>
       <c r="M8" s="3">
         <v>46300</v>
       </c>
       <c r="N8" s="3">
-        <v>48200</v>
+        <v>46300</v>
       </c>
       <c r="O8" s="3">
         <v>48200</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>48200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -804,49 +811,55 @@
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E10" s="3">
         <v>51400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>52100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>53100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>49400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>52300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>47700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>46300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>48900</v>
-      </c>
-      <c r="L10" s="3">
-        <v>46300</v>
       </c>
       <c r="M10" s="3">
         <v>46300</v>
       </c>
       <c r="N10" s="3">
-        <v>48200</v>
+        <v>46300</v>
       </c>
       <c r="O10" s="3">
         <v>48200</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3">
+        <v>48200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,8 +875,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -903,8 +917,11 @@
       <c r="O12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,28 +961,31 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
         <v>-100</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>5</v>
@@ -973,61 +993,67 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>-8900</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M14" s="3">
         <v>-8900</v>
       </c>
       <c r="N14" s="3">
-        <v>-1100</v>
+        <v>-8900</v>
       </c>
       <c r="O14" s="3">
         <v>-1100</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>-1100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E15" s="3">
         <v>1800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1400</v>
-      </c>
-      <c r="F15" s="3">
-        <v>2300</v>
       </c>
       <c r="G15" s="3">
         <v>2300</v>
       </c>
       <c r="H15" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I15" s="3">
         <v>1400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2800</v>
-      </c>
-      <c r="L15" s="3">
-        <v>3400</v>
       </c>
       <c r="M15" s="3">
         <v>3400</v>
       </c>
       <c r="N15" s="3">
-        <v>2700</v>
+        <v>3400</v>
       </c>
       <c r="O15" s="3">
         <v>2700</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1040,90 +1066,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E17" s="3">
         <v>30800</v>
-      </c>
-      <c r="E17" s="3">
-        <v>30400</v>
       </c>
       <c r="F17" s="3">
         <v>30400</v>
       </c>
       <c r="G17" s="3">
+        <v>30400</v>
+      </c>
+      <c r="H17" s="3">
         <v>29900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>32900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>29700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>29400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>28500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>28000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>28200</v>
-      </c>
-      <c r="N17" s="3">
-        <v>28000</v>
       </c>
       <c r="O17" s="3">
         <v>28000</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E18" s="3">
         <v>20600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>21700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>22700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>19500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>19400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>18000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>16900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>20300</v>
-      </c>
-      <c r="L18" s="3">
-        <v>18200</v>
       </c>
       <c r="M18" s="3">
         <v>18200</v>
       </c>
       <c r="N18" s="3">
-        <v>20200</v>
+        <v>18200</v>
       </c>
       <c r="O18" s="3">
         <v>20200</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3">
+        <v>20200</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1139,8 +1172,9 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1154,25 +1188,25 @@
         <v>900</v>
       </c>
       <c r="G20" s="3">
+        <v>900</v>
+      </c>
+      <c r="H20" s="3">
         <v>1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2100</v>
-      </c>
-      <c r="M20" s="3">
-        <v>1600</v>
       </c>
       <c r="N20" s="3">
         <v>1600</v>
@@ -1180,49 +1214,55 @@
       <c r="O20" s="3">
         <v>1600</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E21" s="3">
         <v>21600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>22200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>24100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>20700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>19600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>19500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>18200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>21800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>19600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>20100</v>
-      </c>
-      <c r="N21" s="3">
-        <v>21400</v>
       </c>
       <c r="O21" s="3">
         <v>21400</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3">
+        <v>21400</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1262,90 +1302,99 @@
       <c r="O22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E23" s="3">
         <v>19800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>20900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>21800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>18400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>18300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>16800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>15800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>19000</v>
-      </c>
-      <c r="L23" s="3">
-        <v>25100</v>
       </c>
       <c r="M23" s="3">
         <v>25100</v>
       </c>
       <c r="N23" s="3">
-        <v>18700</v>
+        <v>25100</v>
       </c>
       <c r="O23" s="3">
         <v>18700</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3">
+        <v>18700</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E24" s="3">
         <v>3700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3900</v>
-      </c>
-      <c r="L24" s="3">
-        <v>5100</v>
       </c>
       <c r="M24" s="3">
         <v>5100</v>
       </c>
       <c r="N24" s="3">
-        <v>3800</v>
+        <v>5100</v>
       </c>
       <c r="O24" s="3">
         <v>3800</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1385,90 +1434,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E26" s="3">
         <v>16100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>16500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>17200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>14500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>14200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>13100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>12400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>15100</v>
-      </c>
-      <c r="L26" s="3">
-        <v>20000</v>
       </c>
       <c r="M26" s="3">
         <v>20000</v>
       </c>
       <c r="N26" s="3">
-        <v>14800</v>
+        <v>20000</v>
       </c>
       <c r="O26" s="3">
         <v>14800</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E27" s="3">
         <v>16000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>16300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>17000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>14400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>14100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>13000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>12300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>14900</v>
-      </c>
-      <c r="L27" s="3">
-        <v>19900</v>
       </c>
       <c r="M27" s="3">
         <v>19900</v>
       </c>
       <c r="N27" s="3">
-        <v>14700</v>
+        <v>19900</v>
       </c>
       <c r="O27" s="3">
         <v>14700</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3">
+        <v>14700</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1508,8 +1566,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1549,8 +1610,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1590,8 +1654,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1631,8 +1698,11 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1646,25 +1716,25 @@
         <v>-900</v>
       </c>
       <c r="G32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H32" s="3">
         <v>-1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-1600</v>
       </c>
       <c r="N32" s="3">
         <v>-1600</v>
@@ -1672,49 +1742,55 @@
       <c r="O32" s="3">
         <v>-1600</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3">
+        <v>-1600</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E33" s="3">
         <v>16100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>16500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>17200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>14500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>14200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>13100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>12400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>15100</v>
-      </c>
-      <c r="L33" s="3">
-        <v>20000</v>
       </c>
       <c r="M33" s="3">
         <v>20000</v>
       </c>
       <c r="N33" s="3">
-        <v>14800</v>
+        <v>20000</v>
       </c>
       <c r="O33" s="3">
         <v>14800</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1754,95 +1830,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E35" s="3">
         <v>16100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>16500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>17200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>14500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>14200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>13100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>12400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>15100</v>
-      </c>
-      <c r="L35" s="3">
-        <v>20000</v>
       </c>
       <c r="M35" s="3">
         <v>20000</v>
       </c>
       <c r="N35" s="3">
-        <v>14800</v>
+        <v>20000</v>
       </c>
       <c r="O35" s="3">
         <v>14800</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
-      </c>
-      <c r="L38" s="2">
-        <v>45291</v>
       </c>
       <c r="M38" s="2">
         <v>45291</v>
       </c>
       <c r="N38" s="2">
-        <v>45199</v>
+        <v>45291</v>
       </c>
       <c r="O38" s="2">
         <v>45199</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2">
+        <v>45199</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1858,8 +1943,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1875,90 +1961,97 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>300700</v>
+      </c>
+      <c r="E41" s="3">
         <v>324700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>315800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>297200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>299800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>279200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>293500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>294200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>380500</v>
-      </c>
-      <c r="L41" s="3">
-        <v>347100</v>
       </c>
       <c r="M41" s="3">
         <v>347100</v>
       </c>
       <c r="N41" s="3">
-        <v>325000</v>
+        <v>347100</v>
       </c>
       <c r="O41" s="3">
         <v>325000</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3">
+        <v>325000</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E42" s="3">
         <v>18800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>20800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>23300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>25800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>28500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>29300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>32100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>33600</v>
-      </c>
-      <c r="L42" s="3">
-        <v>34700</v>
       </c>
       <c r="M42" s="3">
         <v>34700</v>
       </c>
       <c r="N42" s="3">
-        <v>35400</v>
+        <v>34700</v>
       </c>
       <c r="O42" s="3">
         <v>35400</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>35400</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1998,8 +2091,11 @@
       <c r="O43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2039,34 +2135,37 @@
       <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E45" s="3">
         <v>16000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>17700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>17200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>18300</v>
       </c>
       <c r="H45" s="3">
         <v>18300</v>
       </c>
       <c r="I45" s="3">
+        <v>18300</v>
+      </c>
+      <c r="J45" s="3">
         <v>17500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>18400</v>
-      </c>
-      <c r="K45" s="3">
-        <v>16900</v>
       </c>
       <c r="L45" s="3">
         <v>16900</v>
@@ -2075,177 +2174,192 @@
         <v>16900</v>
       </c>
       <c r="N45" s="3">
-        <v>16500</v>
+        <v>16900</v>
       </c>
       <c r="O45" s="3">
         <v>16500</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>437400</v>
+      </c>
+      <c r="E46" s="3">
         <v>565200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>551300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>508600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>497200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>532300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>533000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>571300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>654500</v>
-      </c>
-      <c r="L46" s="3">
-        <v>600600</v>
       </c>
       <c r="M46" s="3">
         <v>600600</v>
       </c>
       <c r="N46" s="3">
-        <v>582400</v>
+        <v>600600</v>
       </c>
       <c r="O46" s="3">
         <v>582400</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>582400</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>182800</v>
+      </c>
+      <c r="E47" s="3">
         <v>164800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>178400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>176900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>181900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>180800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>174400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>169200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>149100</v>
-      </c>
-      <c r="L47" s="3">
-        <v>159100</v>
       </c>
       <c r="M47" s="3">
         <v>159100</v>
       </c>
       <c r="N47" s="3">
-        <v>168500</v>
+        <v>159100</v>
       </c>
       <c r="O47" s="3">
         <v>168500</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>168500</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>92800</v>
+      </c>
+      <c r="E48" s="3">
         <v>95400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>97600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>70600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>78700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>109500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>111800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>112900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>109300</v>
-      </c>
-      <c r="L48" s="3">
-        <v>110300</v>
       </c>
       <c r="M48" s="3">
         <v>110300</v>
       </c>
       <c r="N48" s="3">
-        <v>106200</v>
+        <v>110300</v>
       </c>
       <c r="O48" s="3">
         <v>106200</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3">
+        <v>106200</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E49" s="3">
         <v>39000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>39400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>39800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>40200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>40700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>41300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>41800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>42400</v>
-      </c>
-      <c r="L49" s="3">
-        <v>43200</v>
       </c>
       <c r="M49" s="3">
         <v>43200</v>
       </c>
       <c r="N49" s="3">
-        <v>44000</v>
+        <v>43200</v>
       </c>
       <c r="O49" s="3">
         <v>44000</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>44000</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2285,8 +2399,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2326,49 +2443,55 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>120200</v>
+      </c>
+      <c r="E52" s="3">
         <v>134700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>115100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>144300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>146900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>118400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>115900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>112800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>116900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>156300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>195700</v>
-      </c>
-      <c r="N52" s="3">
-        <v>128800</v>
       </c>
       <c r="O52" s="3">
         <v>128800</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>128800</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2408,49 +2531,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4386300</v>
+      </c>
+      <c r="E54" s="3">
         <v>4545600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4592100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4578100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4558100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4595400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4637300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4670900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4684000</v>
-      </c>
-      <c r="L54" s="3">
-        <v>4672600</v>
       </c>
       <c r="M54" s="3">
         <v>4672600</v>
       </c>
       <c r="N54" s="3">
-        <v>4652000</v>
+        <v>4672600</v>
       </c>
       <c r="O54" s="3">
         <v>4652000</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3">
+        <v>4652000</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2466,8 +2595,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2483,90 +2613,97 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3639500</v>
+      </c>
+      <c r="E57" s="3">
         <v>3710000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3698200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3666200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3736400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3779200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3761600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3707800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3799800</v>
-      </c>
-      <c r="L57" s="3">
-        <v>3661400</v>
       </c>
       <c r="M57" s="3">
         <v>3661400</v>
       </c>
       <c r="N57" s="3">
-        <v>3641000</v>
+        <v>3661400</v>
       </c>
       <c r="O57" s="3">
         <v>3641000</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3">
+        <v>3641000</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>91400</v>
+      </c>
+      <c r="E58" s="3">
         <v>166900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>230500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>265900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>178400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>188000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>254500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>353800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>277400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>415000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>433800</v>
-      </c>
-      <c r="N58" s="3">
-        <v>453600</v>
       </c>
       <c r="O58" s="3">
         <v>453600</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>453600</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2606,131 +2743,143 @@
       <c r="O59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3731000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3876900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3928700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3932100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3914700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3967200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4016000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4061600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4077200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4076400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4095100</v>
-      </c>
-      <c r="N60" s="3">
-        <v>4094600</v>
       </c>
       <c r="O60" s="3">
         <v>4094600</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>4094600</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E61" s="3">
         <v>17400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>19200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>18700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>18400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>19700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>25600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>31100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>34800</v>
-      </c>
-      <c r="L61" s="3">
-        <v>39800</v>
       </c>
       <c r="M61" s="3">
         <v>39800</v>
       </c>
       <c r="N61" s="3">
-        <v>19900</v>
+        <v>39800</v>
       </c>
       <c r="O61" s="3">
         <v>19900</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>19900</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E62" s="3">
         <v>45600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>48400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>48000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>59500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>51600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>55700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>54600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>58800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>51300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>67600</v>
-      </c>
-      <c r="N62" s="3">
-        <v>53100</v>
       </c>
       <c r="O62" s="3">
         <v>53100</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>53100</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2770,8 +2919,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2811,8 +2963,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2852,49 +3007,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3793900</v>
+      </c>
+      <c r="E66" s="3">
         <v>3944900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3996300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3998800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3992600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4043700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4097300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4147200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4170800</v>
-      </c>
-      <c r="L66" s="3">
-        <v>4172700</v>
       </c>
       <c r="M66" s="3">
         <v>4172700</v>
       </c>
       <c r="N66" s="3">
-        <v>4167600</v>
+        <v>4172700</v>
       </c>
       <c r="O66" s="3">
         <v>4167600</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3">
+        <v>4167600</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2910,8 +3071,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2951,8 +3113,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2992,8 +3157,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3033,8 +3201,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3074,49 +3245,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>451100</v>
+      </c>
+      <c r="E72" s="3">
         <v>436500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>422600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>408200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>393000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>380500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>368400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>357100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>346600</v>
-      </c>
-      <c r="L72" s="3">
-        <v>333400</v>
       </c>
       <c r="M72" s="3">
         <v>333400</v>
       </c>
       <c r="N72" s="3">
-        <v>321800</v>
+        <v>333400</v>
       </c>
       <c r="O72" s="3">
         <v>321800</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3">
+        <v>321800</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3156,8 +3333,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3197,8 +3377,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3238,49 +3421,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>592400</v>
+      </c>
+      <c r="E76" s="3">
         <v>600700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>595800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>579300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>565400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>551800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>540000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>523600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>513200</v>
-      </c>
-      <c r="L76" s="3">
-        <v>499900</v>
       </c>
       <c r="M76" s="3">
         <v>499900</v>
       </c>
       <c r="N76" s="3">
-        <v>484400</v>
+        <v>499900</v>
       </c>
       <c r="O76" s="3">
         <v>484400</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3">
+        <v>484400</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3320,95 +3509,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
-      </c>
-      <c r="L80" s="2">
-        <v>45291</v>
       </c>
       <c r="M80" s="2">
         <v>45291</v>
       </c>
       <c r="N80" s="2">
-        <v>45199</v>
+        <v>45291</v>
       </c>
       <c r="O80" s="2">
         <v>45199</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2">
+        <v>45199</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E81" s="3">
         <v>16100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>16500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>17200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>14500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>14200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>13100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>12400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>15100</v>
-      </c>
-      <c r="L81" s="3">
-        <v>20000</v>
       </c>
       <c r="M81" s="3">
         <v>20000</v>
       </c>
       <c r="N81" s="3">
-        <v>14800</v>
+        <v>20000</v>
       </c>
       <c r="O81" s="3">
         <v>14800</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3">
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3424,28 +3622,29 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E83" s="3">
         <v>3100</v>
-      </c>
-      <c r="E83" s="3">
-        <v>3000</v>
       </c>
       <c r="F83" s="3">
         <v>3000</v>
       </c>
       <c r="G83" s="3">
+        <v>3000</v>
+      </c>
+      <c r="H83" s="3">
         <v>2600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2700</v>
-      </c>
-      <c r="I83" s="3">
-        <v>2400</v>
       </c>
       <c r="J83" s="3">
         <v>2400</v>
@@ -3460,13 +3659,16 @@
         <v>2400</v>
       </c>
       <c r="N83" s="3">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="O83" s="3">
         <v>2300</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3506,8 +3708,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3547,8 +3752,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3588,8 +3796,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3629,8 +3840,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3670,49 +3884,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>110800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-11300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-8800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>71700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>43800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-9000</v>
-      </c>
-      <c r="L89" s="3">
-        <v>90000</v>
       </c>
       <c r="M89" s="3">
         <v>90000</v>
       </c>
       <c r="N89" s="3">
-        <v>-33000</v>
+        <v>90000</v>
       </c>
       <c r="O89" s="3">
         <v>-33000</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3">
+        <v>-33000</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3728,49 +3948,53 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4000</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-14700</v>
       </c>
       <c r="M91" s="3">
         <v>-14700</v>
       </c>
       <c r="N91" s="3">
-        <v>-5500</v>
+        <v>-14700</v>
       </c>
       <c r="O91" s="3">
         <v>-5500</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>-5500</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3810,8 +4034,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3851,49 +4078,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E94" s="3">
         <v>76900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>34500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6900</v>
       </c>
-      <c r="G94" s="3">
-        <v>5600</v>
-      </c>
       <c r="H94" s="3">
+        <v>5700</v>
+      </c>
+      <c r="I94" s="3">
         <v>37000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>6300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-70700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>48100</v>
-      </c>
-      <c r="L94" s="3">
-        <v>89500</v>
       </c>
       <c r="M94" s="3">
         <v>89500</v>
       </c>
       <c r="N94" s="3">
-        <v>21500</v>
+        <v>89500</v>
       </c>
       <c r="O94" s="3">
         <v>21500</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3">
+        <v>21500</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3909,8 +4142,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3918,7 +4152,7 @@
         <v>2200</v>
       </c>
       <c r="E96" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="F96" s="3">
         <v>2100</v>
@@ -3930,7 +4164,7 @@
         <v>2100</v>
       </c>
       <c r="I96" s="3">
-        <v>1900</v>
+        <v>2100</v>
       </c>
       <c r="J96" s="3">
         <v>1900</v>
@@ -3939,19 +4173,22 @@
         <v>1900</v>
       </c>
       <c r="L96" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="M96" s="3">
         <v>2000</v>
       </c>
       <c r="N96" s="3">
-        <v>1700</v>
+        <v>2000</v>
       </c>
       <c r="O96" s="3">
         <v>1700</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3991,8 +4228,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4032,8 +4272,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4073,49 +4316,55 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-171200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-65900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>13100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-56700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-56000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-50800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-21500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5800</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-252200</v>
       </c>
       <c r="M100" s="3">
         <v>-252200</v>
       </c>
       <c r="N100" s="3">
-        <v>33000</v>
+        <v>-252200</v>
       </c>
       <c r="O100" s="3">
         <v>33000</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4155,45 +4404,51 @@
       <c r="O101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E102" s="3">
         <v>8900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>18600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>20600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-14300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-86300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>33400</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-72700</v>
       </c>
       <c r="M102" s="3">
         <v>-72700</v>
       </c>
       <c r="N102" s="3">
+        <v>-72700</v>
+      </c>
+      <c r="O102" s="3">
         <v>21500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>21500</v>
       </c>
     </row>
